--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/da-metrics-hard.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/da-metrics-hard.xlsx
@@ -466,10 +466,10 @@
         <v>Tỷ lệ LTV : CAC = 4 : 1; mô hình kinh doanh cực kỳ xuất sắc vì vượt qua mốc 3:1, doanh nghiệp nên tăng cường đầu tư mạnh vào marketing — LTV:CAC = 4:1 xuất sắc</v>
       </c>
       <c r="H2" t="str">
+        <v>Tỷ lệ LTV : CAC = 3 : 1; mô hình đạt trạng thái cân bằng hoàn hảo, không cần thay đổi bất kỳ chiến lược nào — LTV:CAC = 3:1 cân bằng</v>
+      </c>
+      <c r="I2" t="str">
         <v>Tỷ lệ LTV : CAC = 0.8 : 1; doanh nghiệp đang bị lỗ trực tiếp trên mỗi khách hàng có được, cần phải tăng giá thuê bao ngay lập tức — LTV:CAC = 0.8:1 lỗ trực tiếp</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Tỷ lệ LTV : CAC = 3 : 1; mô hình đạt trạng thái cân bằng hoàn hảo, không cần thay đổi bất kỳ chiến lược nào — LTV:CAC = 3:1 cân bằng</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -492,19 +492,19 @@
         <v>Nếu đường cong Retention tiếp tục dốc xuống về 0, app của bạn đang bị rò rỉ khách hàng (leaky bucket) và sẽ chết. Nếu đường cong đi ngang và ổn định ở một mức (ví dụ 20% kể từ tháng thứ 3 trở đi), điều đó chứng tỏ bạn đã giữ chân được một lượng người dùng trung thành ổn định, là dấu hiệu đạt Product-Market Fit.</v>
       </c>
       <c r="F3" t="str">
-        <v>Sản phẩm đã đạt được mức độ phù hợp thị trường (Product-Market Fit) đối với một tập khách hàng trung thành nhất định; tỷ lệ giữ chân ổn định ở mức dài hạn — đạt PMF ổn định dài hạn</v>
+        <v>Doanh nghiệp sắp bị phá sản do lượng người dùng mới đăng ký hàng tháng giảm về mức 0 — suy giảm tăng trưởng</v>
       </c>
       <c r="G3" t="str">
         <v>Sản phẩm đang bị lỗi kỹ thuật nghiêm trọng trên production khiến người dùng không thể đăng xuất tài khoản — lỗi hệ thống</v>
       </c>
       <c r="H3" t="str">
-        <v>Doanh nghiệp sắp bị phá sản do lượng người dùng mới đăng ký hàng tháng giảm về mức 0 — suy giảm tăng trưởng</v>
+        <v>Sản phẩm đã đạt được mức độ phù hợp thị trường (Product-Market Fit) đối với một tập khách hàng trung thành nhất định; tỷ lệ giữ chân ổn định ở mức dài hạn — đạt PMF ổn định dài hạn</v>
       </c>
       <c r="I3" t="str">
         <v>Toàn bộ khách hàng cũ đã chuyển sang sử dụng dịch vụ của đối thủ cạnh tranh trực tiếp trên thị trường — mất khách hàng</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>Rất nhiều startup chết vì đặt ngân sách CAC dựa trên LTV thô (doanh thu). Ví dụ: LTV thô = 100 USD, biên lợi nhuận (Gross Margin) chỉ đạt 20% (Net LTV = 20 USD). Nếu thiết lập trần CAC = 40 USD (dựa trên suy nghĩ LTV 100 USD &gt; 40 USD), công ty thực tế đang lỗ ròng 20 USD trên mỗi khách hàng mới.</v>
       </c>
       <c r="F4" t="str">
+        <v>LTV thô bắt buộc phải lớn gấp 100 lần so với Net LTV trong mọi mô hình kinh doanh bán lẻ — quy mô chênh lệch</v>
+      </c>
+      <c r="G4" t="str">
+        <v>LTV thô do phòng Marketing tính toán; Net LTV do phòng IT tự động lập trình trên máy chủ — phân vai trò tính</v>
+      </c>
+      <c r="H4" t="str">
+        <v>LTV thô chỉ dùng cho khách hàng nam; Net LTV chỉ áp dụng cho khách hàng nữ — phân loại khách hàng</v>
+      </c>
+      <c r="I4" t="str">
         <v>LTV thô chỉ tính tổng doanh thu; Net LTV trừ đi giá vốn hàng bán (COGS) và chi phí vận hành; dùng LTV thô để đặt trần chi phí CAC sẽ khiến doanh nghiệp chi tiêu quá tay cho marketing và thực tế bị lỗ ròng — rủi ro thổi phồng ngân sách marketing</v>
       </c>
-      <c r="G4" t="str">
-        <v>LTV thô chỉ dùng cho khách hàng nam; Net LTV chỉ áp dụng cho khách hàng nữ — phân loại khách hàng</v>
-      </c>
-      <c r="H4" t="str">
-        <v>LTV thô do phòng Marketing tính toán; Net LTV do phòng IT tự động lập trình trên máy chủ — phân vai trò tính</v>
-      </c>
-      <c r="I4" t="str">
-        <v>LTV thô bắt buộc phải lớn gấp 100 lần so với Net LTV trong mọi mô hình kinh doanh bán lẻ — quy mô chênh lệch</v>
-      </c>
       <c r="J4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>SaaS Quick Ratio đo lường hiệu quả tăng trưởng ARR. Nó so sánh phần ARR tăng thêm (khách mới + upsell khách cũ) với phần ARR bị mất đi (khách hạ gói + khách hủy thuê bao). Tỷ lệ Quick Ratio &gt; 4 chứng tỏ tốc độ tăng trưởng nhanh gấp 4 lần tốc độ mất mát doanh thu, thể hiện doanh nghiệp phát triển cực kỳ khỏe mạnh.</v>
       </c>
       <c r="F5" t="str">
+        <v>$\text{Quick Ratio} = \text{Tốc độ tải trang chủ} / \text{Tốc độ tải trang thanh toán}$; đo lường hiệu năng tải trang web — tốc độ tải trang</v>
+      </c>
+      <c r="G5" t="str">
         <v>$\text{Quick Ratio} = (\text{New ARR} + \text{Expansion ARR}) / (\text{Contraction ARR} + \text{Churn ARR})$; thể hiện khả năng tăng trưởng doanh thu định kỳ bất chấp sự mất mát khách hàng (Quick Ratio &gt; 4 được coi là xuất sắc) — chỉ số đo lường hiệu năng tăng trưởng ARR</v>
-      </c>
-      <c r="G5" t="str">
-        <v>$\text{Quick Ratio} = \text{Tổng tài sản ngắn hạn} / \text{Tổng nợ ngắn hạn}$; đo lường khả năng thanh toán nhanh các khoản nợ của doanh nghiệp — thanh toán tài chính doanh nghiệp</v>
       </c>
       <c r="H5" t="str">
         <v>$\text{Quick Ratio} = \text{Số lượng bug được sửa trong ngày} / \text{Tổng số lượng bug phát sinh}$; đo lường năng suất sửa lỗi của dev — năng suất sửa bug</v>
       </c>
       <c r="I5" t="str">
-        <v>$\text{Quick Ratio} = \text{Tốc độ tải trang chủ} / \text{Tốc độ tải trang thanh toán}$; đo lường hiệu năng tải trang web — tốc độ tải trang</v>
+        <v>$\text{Quick Ratio} = \text{Tổng tài sản ngắn hạn} / \text{Tổng nợ ngắn hạn}$; đo lường khả năng thanh toán nhanh các khoản nợ của doanh nghiệp — thanh toán tài chính doanh nghiệp</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>Công thức K-factor: $K = c \cdot i$, với $c$ là số lời mời trung bình gửi đi bởi 1 khách hàng, $i$ là tỷ lệ chuyển đổi lời mời thành công. Nếu $K = 1.2$ ($&gt;1$), cứ 100 người dùng ban đầu sẽ tự động mời được 120 người mới, 120 người đó mời tiếp 144 người... tạo ra hiệu ứng lan truyền (Virality) khổng lồ.</v>
       </c>
       <c r="F6" t="str">
+        <v>K-factor đo lường số lần người dùng mở ứng dụng di động trong một giờ cao điểm — tần suất mở ứng dụng</v>
+      </c>
+      <c r="G6" t="str">
+        <v>K-factor đo lường dung lượng lưu trữ trung bình của ứng dụng khi cài đặt trên điện thoại di động — dung lượng cài đặt</v>
+      </c>
+      <c r="H6" t="str">
+        <v>K-factor đo lường số lượng lỗi kỹ thuật phát sinh trên mỗi 1000 dòng code của lập trình viên — chỉ số lỗi code</v>
+      </c>
+      <c r="I6" t="str">
         <v>K-factor đo lường số lượng người dùng mới được mời thành công bởi mỗi người dùng hiện tại; nếu $K &gt; 1$, ứng dụng sẽ tự động tăng trưởng theo cấp số nhân một cách tự nhiên mà không cần chạy ads quảng cáo — hệ số lan truyền virus</v>
       </c>
-      <c r="G6" t="str">
-        <v>K-factor đo lường số lượng lỗi kỹ thuật phát sinh trên mỗi 1000 dòng code của lập trình viên — chỉ số lỗi code</v>
-      </c>
-      <c r="H6" t="str">
-        <v>K-factor đo lường dung lượng lưu trữ trung bình của ứng dụng khi cài đặt trên điện thoại di động — dung lượng cài đặt</v>
-      </c>
-      <c r="I6" t="str">
-        <v>K-factor đo lường số lần người dùng mở ứng dụng di động trong một giờ cao điểm — tần suất mở ứng dụng</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -623,10 +623,10 @@
         <v>Vì doanh thu thô chưa trừ đi giá vốn hàng bán và chi phí vận hành trực tiếp; dùng doanh thu thô làm thời gian hoàn vốn thực tế trên giấy tờ có vẻ ngắn nhưng doanh nghiệp vẫn có thể bị cạn kiệt dòng tiền mặt thực tế — tính toán hoàn vốn dựa trên lợi nhuận gộp</v>
       </c>
       <c r="G7" t="str">
+        <v>Vì doanh thu thô bắt buộc phải được quy đổi sang đồng tiền USD trước khi thực hiện tính toán hoàn vốn — quy đổi tiền tệ</v>
+      </c>
+      <c r="H7" t="str">
         <v>Vì lợi nhuận gộp là chỉ số phi chức năng còn doanh thu thô luôn là chỉ số chức năng kinh doanh — phân loại chỉ số</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Vì doanh thu thô bắt buộc phải được quy đổi sang đồng tiền USD trước khi thực hiện tính toán hoàn vốn — quy đổi tiền tệ</v>
       </c>
       <c r="I7" t="str">
         <v>Vì thời gian hoàn vốn chỉ được phép tính toán đối với các dự án đã hoạt động trên 10 năm — giới hạn tuổi dự án</v>
@@ -652,19 +652,19 @@
         <v>NRR &lt; 100% (ở đây là 75%) có nghĩa là doanh nghiệp đang bị mất đi 25% doanh thu từ tập khách hàng cũ sau mỗi năm (do họ hủy gói hoặc giảm cấp dịch vụ). Tăng trưởng nhanh nhờ khách mới chỉ là bề nổi che lấp sự rò rỉ dữ liệu. Khi chi phí mua khách mới (CAC) tăng lên hoặc cạn kiệt thị trường, doanh nghiệp sẽ sụp đổ nhanh chóng.</v>
       </c>
       <c r="F8" t="str">
+        <v>Doanh nghiệp đang vận hành cực kỳ khỏe mạnh và bền vững do số lượng khách hàng mới tăng trưởng liên tục — đánh giá bề mặt sai lệch</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Doanh nghiệp sắp đạt mốc IPO trên sàn chứng khoán quốc tế nhờ doanh thu tăng trưởng ổn định — nhận định lạc quan quá mức</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Sản phẩm đã đạt mốc Product-Market Fit hoàn hảo và không cần cải tiến thêm bất kỳ tính năng nào — nhận định sai thực tế</v>
+      </c>
+      <c r="I8" t="str">
         <v>Doanh nghiệp đang gặp vấn đề nghiêm trọng về giữ chân khách hàng (High Churn Rate ở tập khách hàng cũ); sự tăng trưởng hiện tại chỉ dựa vào việc đốt tiền mua khách mới để lấp đầy lỗ hổng (Leaky Bucket) — tăng trưởng không bền vững do Churn cao</v>
       </c>
-      <c r="G8" t="str">
-        <v>Doanh nghiệp đang vận hành cực kỳ khỏe mạnh và bền vững do số lượng khách hàng mới tăng trưởng liên tục — đánh giá bề mặt sai lệch</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Doanh nghiệp sắp đạt mốc IPO trên sàn chứng khoán quốc tế nhờ doanh thu tăng trưởng ổn định — nhận định lạc quan quá mức</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Sản phẩm đã đạt mốc Product-Market Fit hoàn hảo và không cần cải tiến thêm bất kỳ tính năng nào — nhận định sai thực tế</v>
-      </c>
       <c r="J8">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>Độ co giãn của cầu theo giá giúp doanh nghiệp đưa ra chiến lược định giá (Pricing Strategy) khoa học. Cầu co giãn ($|E| &gt; 1$) nghĩa là khách hàng rất nhạy cảm với giá (ví dụ: tăng giá 10% làm giảm 20% lượng mua, dẫn đến tổng doanh thu giảm). Cầu ít co giãn ($|E| &lt; 1$, như thuốc chữa bệnh) cho phép tăng giá để tăng tổng doanh thu.</v>
       </c>
       <c r="F9" t="str">
+        <v>Đo lường tốc độ giao hàng trung bình của chuỗi cung ứng khi giá xăng dầu biến động — tốc độ vận chuyển chuỗi cung ứng</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Tính toán số lượng nhân viên tối đa cần sa thải để duy trì lợi nhuận ròng ổn định cho công ty — tối ưu hóa nhân sự</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Đo lường chi phí sản xuất trung bình của một sản phẩm khi số lượng đặt hàng tăng lên — hiệu ứng quy mô sản xuất</v>
+      </c>
+      <c r="I9" t="str">
         <v>Đo lường mức độ nhạy cảm của nhu cầu lượng mua sản phẩm khi giá bán thay đổi; nếu $|E| &gt; 1$ (cầu co giãn), việc tăng giá sẽ làm giảm tổng doanh thu do lượng cầu giảm mạnh hơn tốc độ tăng giá — độ co giãn của cầu theo giá</v>
       </c>
-      <c r="G9" t="str">
-        <v>Đo lường chi phí sản xuất trung bình của một sản phẩm khi số lượng đặt hàng tăng lên — hiệu ứng quy mô sản xuất</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Đo lường tốc độ giao hàng trung bình của chuỗi cung ứng khi giá xăng dầu biến động — tốc độ vận chuyển chuỗi cung ứng</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Tính toán số lượng nhân viên tối đa cần sa thải để duy trì lợi nhuận ròng ổn định cho công ty — tối ưu hóa nhân sự</v>
-      </c>
       <c r="J9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -719,13 +719,13 @@
         <v>Tính dựa trên ARPU, Gross Margin và Churn Rate; giả định hành vi rời bỏ tuân theo phân phối hình học (Geometric Distribution) với xác suất rời bỏ không đổi qua các kỳ — công thức tính LTV và giả định phân phối</v>
       </c>
       <c r="G10" t="str">
+        <v>Tính dựa trên số dòng code, số lượng bug và dung lượng RAM máy chủ; giả định phân phối Poisson — các tham số kỹ thuật</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Tính dựa trên tổng tài sản ngắn hạn và nợ phải trả của doanh nghiệp; giả định phân phối đều — các tham số tài chính doanh nghiệp</v>
+      </c>
+      <c r="I10" t="str">
         <v>Tính dựa trên chi phí marketing, số lượng nhân viên sales và thời gian bảo hành sản phẩm; giả định phân phối chuẩn — các tham số sai lệch</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Tính dựa trên số dòng code, số lượng bug và dung lượng RAM máy chủ; giả định phân phối Poisson — các tham số kỹ thuật</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Tính dựa trên tổng tài sản ngắn hạn và nợ phải trả của doanh nghiệp; giả định phân phối đều — các tham số tài chính doanh nghiệp</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -754,10 +754,10 @@
         <v>Last Touch bắt buộc doanh nghiệp phải trả phí hoa hồng cao hơn gấp 10 lần cho các đại lý quảng cáo — tăng chi phí hoa hồng</v>
       </c>
       <c r="H11" t="str">
+        <v>Last Touch chỉ hỗ trợ ghi nhận doanh thu đối với khách hàng mua hàng vào ban ngày — giới hạn thời gian mua hàng</v>
+      </c>
+      <c r="I11" t="str">
         <v>Last Touch làm chậm tốc độ tải trang của hệ thống báo cáo dashboard PowerBI — chậm hiệu năng dashboard</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Last Touch chỉ hỗ trợ ghi nhận doanh thu đối với khách hàng mua hàng vào ban ngày — giới hạn thời gian mua hàng</v>
       </c>
       <c r="J11">
         <v>1</v>
